--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,34 +44,25 @@
     <t xml:space="preserve">Venue</t>
   </si>
   <si>
-    <t xml:space="preserve">hawthorn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne</t>
+    <t xml:space="preserve">north melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geelong cats</t>
   </si>
   <si>
     <t xml:space="preserve">Provisional</t>
   </si>
   <si>
+    <t xml:space="preserve">Marvel Stadium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">richmond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collingwood</t>
+  </si>
+  <si>
     <t xml:space="preserve">IKON Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geelong cats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marvel Stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">richmond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collingwood</t>
   </si>
   <si>
     <t xml:space="preserve">gold coast suns</t>
@@ -497,7 +488,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -512,16 +503,16 @@
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>28.4</v>
+        <v>-42</v>
       </c>
       <c r="G2" t="n">
-        <v>13.3</v>
+        <v>-25</v>
       </c>
       <c r="H2" t="n">
-        <v>30.9</v>
+        <v>-47.3</v>
       </c>
       <c r="I2" t="n">
-        <v>82.9</v>
+        <v>86.2</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -538,25 +529,25 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>73.9</v>
+      </c>
+      <c r="J3" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-47.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-51.8</v>
-      </c>
-      <c r="I3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -564,36 +555,36 @@
         <v>46249</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>80.9</v>
+      </c>
+      <c r="J4" t="s">
         <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H4" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="I4" t="n">
-        <v>73.9</v>
-      </c>
-      <c r="J4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -602,22 +593,22 @@
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="G5" t="n">
-        <v>19.2</v>
+        <v>17.8</v>
       </c>
       <c r="H5" t="n">
-        <v>32.1</v>
+        <v>25.1</v>
       </c>
       <c r="I5" t="n">
-        <v>80.9</v>
+        <v>79.6</v>
       </c>
       <c r="J5" t="s">
         <v>22</v>
@@ -634,22 +625,22 @@
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>1.7</v>
       </c>
       <c r="G6" t="n">
-        <v>17.8</v>
+        <v>-5.8</v>
       </c>
       <c r="H6" t="n">
-        <v>45.5</v>
+        <v>6.1</v>
       </c>
       <c r="I6" t="n">
-        <v>79.6</v>
+        <v>83.5</v>
       </c>
       <c r="J6" t="s">
         <v>25</v>
@@ -666,22 +657,22 @@
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>-20.8</v>
+        <v>-4.1</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.8</v>
+        <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>-22.3</v>
+        <v>-0.4</v>
       </c>
       <c r="I7" t="n">
-        <v>83.5</v>
+        <v>87.5</v>
       </c>
       <c r="J7" t="s">
         <v>28</v>
@@ -698,57 +689,25 @@
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.6</v>
+        <v>6.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>8.8</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5</v>
+        <v>6.7</v>
       </c>
       <c r="I8" t="n">
-        <v>87.5</v>
+        <v>82.7</v>
       </c>
       <c r="J8" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8.8</v>
-      </c>
-      <c r="H9" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="J9" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,36 +12,132 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Team List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Team List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROD Projected Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM-only Projected Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLAYER-only Projected Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projected Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venue</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+  <si>
+    <t xml:space="preserve">rating_as_of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_datetime_utc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model_version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected_margin_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prod_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prod_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">previous_prod_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_only_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_only_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_home_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_away_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hybrid_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hybrid_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hybrid_weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">binary_preferred_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">binary_preferred_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">significant_change_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_team_disagreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_lineup_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_lineup_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_team_list_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_team_list_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cold_start_players</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_team_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_player_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_lineup_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_team_lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_player_lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_decay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-15T03:00:00.000+0000</t>
   </si>
   <si>
     <t xml:space="preserve">north melbourne</t>
@@ -50,10 +146,22 @@
     <t xml:space="preserve">geelong cats</t>
   </si>
   <si>
+    <t xml:space="preserve">Marvel Stadium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aflw_joint_club_persistent_player_margin_prod_1.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOINT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Provisional</t>
   </si>
   <si>
-    <t xml:space="preserve">Marvel Stadium</t>
+    <t xml:space="preserve">2026-08-15T07:05:00.000+0000</t>
   </si>
   <si>
     <t xml:space="preserve">richmond</t>
@@ -65,6 +173,9 @@
     <t xml:space="preserve">IKON Park</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-08-15T09:15:00.000+0000</t>
+  </si>
+  <si>
     <t xml:space="preserve">gold coast suns</t>
   </si>
   <si>
@@ -74,6 +185,9 @@
     <t xml:space="preserve">People First Stadium</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-08-16T02:35:00.000+0000</t>
+  </si>
+  <si>
     <t xml:space="preserve">essendon</t>
   </si>
   <si>
@@ -92,6 +206,9 @@
     <t xml:space="preserve">Unley Oval</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-08-16T04:35:00.000+0000</t>
+  </si>
+  <si>
     <t xml:space="preserve">fremantle</t>
   </si>
   <si>
@@ -99,6 +216,9 @@
   </si>
   <si>
     <t xml:space="preserve">Cockburn ARC Oval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16T06:45:00.000+0000</t>
   </si>
   <si>
     <t xml:space="preserve">greater western sydney</t>
@@ -442,16 +562,47 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="17.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="19.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="26.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="20.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="5.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="17.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="20.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="51.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="21.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="14.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="12.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="15.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="20.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="16.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="19.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="18.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="21.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="15.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="20.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="20.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="13.71" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="16.71" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="13.71" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="22.71" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="23.71" hidden="0" customWidth="1"/>
+    <col min="27" max="27" width="15.71" hidden="0" customWidth="1"/>
+    <col min="28" max="28" width="23.71" hidden="0" customWidth="1"/>
+    <col min="29" max="29" width="24.71" hidden="0" customWidth="1"/>
+    <col min="30" max="30" width="18.71" hidden="0" customWidth="1"/>
+    <col min="31" max="31" width="18.71" hidden="0" customWidth="1"/>
+    <col min="32" max="32" width="21.71" hidden="0" customWidth="1"/>
+    <col min="33" max="33" width="21.71" hidden="0" customWidth="1"/>
+    <col min="34" max="34" width="18.71" hidden="0" customWidth="1"/>
+    <col min="35" max="35" width="14.71" hidden="0" customWidth="1"/>
+    <col min="36" max="36" width="20.71" hidden="0" customWidth="1"/>
+    <col min="37" max="37" width="22.71" hidden="0" customWidth="1"/>
+    <col min="38" max="38" width="21.71" hidden="0" customWidth="1"/>
+    <col min="39" max="39" width="17.71" hidden="0" customWidth="1"/>
+    <col min="40" max="40" width="19.71" hidden="0" customWidth="1"/>
+    <col min="41" max="41" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -485,229 +636,973 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>46249</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
       <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
+        <v>41</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-42</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-47.3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="J2" t="s">
-        <v>13</v>
+        <v>42</v>
+      </c>
+      <c r="F2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" t="n">
+        <v>41.9603759515757</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-41.9603759515757</v>
+      </c>
+      <c r="L2" t="n">
+        <v>41.9603759515757</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-41.9603759515757</v>
+      </c>
+      <c r="N2" t="n">
+        <v>41.9603759515757</v>
+      </c>
+      <c r="O2" t="n">
+        <v>24.9522195073725</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-24.9522195073725</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>47.3382799386634</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-47.3382799386634</v>
+      </c>
+      <c r="S2" t="n">
+        <v>86.2238773235671</v>
+      </c>
+      <c r="T2" t="n">
+        <v>64.0921266375714</v>
+      </c>
+      <c r="U2" t="n">
+        <v>22.1317506859957</v>
+      </c>
+      <c r="V2" t="n">
+        <v>32.7999170967689</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-32.7999170967689</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.350561797752809</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>24.9522195073725</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.887640449438202</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>22.3860604312909</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>10.1493261981839</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>31.8110497533917</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.887640449438202</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>46249</v>
       </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
       <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
+        <v>49</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>73.9</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
+        <v>50</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.97754654342604</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.97754654342604</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.97754654342604</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.97754654342604</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.97754654342604</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.6529815470056</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.6529815470056</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-2.16724610263217</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.16724610263217</v>
+      </c>
+      <c r="S3" t="n">
+        <v>73.8697103945514</v>
+      </c>
+      <c r="T3" t="n">
+        <v>36.4460819255627</v>
+      </c>
+      <c r="U3" t="n">
+        <v>37.4236284689887</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.6529815470056</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.6529815470056</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.6529815470056</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.76485956890921</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-1.51426455562657</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>7.49376902387064</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-8.47131556729668</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.76485956890921</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>46249</v>
       </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
       <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
+        <v>53</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="I4" t="n">
-        <v>80.9</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7.82392021935796</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-7.82392021935796</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7.82392021935796</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-7.82392021935796</v>
+      </c>
+      <c r="N4" t="n">
+        <v>7.82392021935796</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-19.162220862405</v>
+      </c>
+      <c r="P4" t="n">
+        <v>19.162220862405</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.842182482803</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-1.842182482803</v>
+      </c>
+      <c r="S4" t="n">
+        <v>80.9237449518709</v>
+      </c>
+      <c r="T4" t="n">
+        <v>44.3738325856144</v>
+      </c>
+      <c r="U4" t="n">
+        <v>36.5499123662565</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-19.162220862405</v>
+      </c>
+      <c r="W4" t="n">
+        <v>19.162220862405</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-19.162220862405</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.597044996642042</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>21.004403345208</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-13.7687908788691</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>21.592711098227</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.597044996642042</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B5" s="1" t="n">
         <v>46250</v>
       </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
       <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
+        <v>57</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H5" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>79.6</v>
-      </c>
-      <c r="J5" t="s">
-        <v>22</v>
+        <v>58</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-22.4729347430033</v>
+      </c>
+      <c r="K5" t="n">
+        <v>22.4729347430033</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-22.4729347430033</v>
+      </c>
+      <c r="M5" t="n">
+        <v>22.4729347430033</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-22.4729347430033</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-17.7771541219833</v>
+      </c>
+      <c r="P5" t="n">
+        <v>17.7771541219833</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-25.0555803252431</v>
+      </c>
+      <c r="R5" t="n">
+        <v>25.0555803252431</v>
+      </c>
+      <c r="S5" t="n">
+        <v>79.5600132867297</v>
+      </c>
+      <c r="T5" t="n">
+        <v>28.5435392718632</v>
+      </c>
+      <c r="U5" t="n">
+        <v>51.0164740148665</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-20.6885246032872</v>
+      </c>
+      <c r="W5" t="n">
+        <v>20.6885246032872</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-17.7771541219833</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.926244622003688</v>
+      </c>
+      <c r="AB5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-7.27842620325976</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-8.74631109085783</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-13.7266236521454</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.926244622003688</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B6" s="1" t="n">
         <v>46250</v>
       </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
       <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
+        <v>57</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-5.8</v>
-      </c>
-      <c r="H6" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="J6" t="s">
-        <v>25</v>
+        <v>61</v>
+      </c>
+      <c r="F6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1.69859465949529</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.69859465949529</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-1.69859465949529</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.69859465949529</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1.69859465949529</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5.78563699612798</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-5.78563699612798</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-6.12261561198919</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6.12261561198919</v>
+      </c>
+      <c r="S6" t="n">
+        <v>83.4884649131954</v>
+      </c>
+      <c r="T6" t="n">
+        <v>40.8949351268501</v>
+      </c>
+      <c r="U6" t="n">
+        <v>42.5935297863453</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.74109493383141</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-1.74109493383141</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.339641943734015</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5.78563699612798</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.884910485933504</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-11.9082526081172</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>5.19062435248488</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-6.88921901198017</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.884910485933504</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B7" s="1" t="n">
         <v>46250</v>
       </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
       <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="J7" t="s">
-        <v>28</v>
+        <v>65</v>
+      </c>
+      <c r="F7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.13970433545176</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-4.13970433545176</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4.13970433545176</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-4.13970433545176</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.13970433545176</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-2.55150894757409</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.55150894757409</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.427793645196616</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.427793645196616</v>
+      </c>
+      <c r="S7" t="n">
+        <v>87.5121821932886</v>
+      </c>
+      <c r="T7" t="n">
+        <v>45.8259432643702</v>
+      </c>
+      <c r="U7" t="n">
+        <v>41.6862389289184</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-1.35978791046581</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.35978791046581</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-2.55150894757409</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.924480805538074</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.97930259277071</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-10.8035824180116</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>14.9432867534633</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.924480805538074</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B8" s="1" t="n">
         <v>46250</v>
       </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
       <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
+        <v>68</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8.8</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I8" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="J8" t="s">
-        <v>31</v>
+        <v>69</v>
+      </c>
+      <c r="F8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-6.2099375493025</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.2099375493025</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-6.2099375493025</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6.2099375493025</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-6.2099375493025</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-8.81497792845377</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8.81497792845377</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-6.73825942275811</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6.73825942275811</v>
+      </c>
+      <c r="S8" t="n">
+        <v>82.6952099754759</v>
+      </c>
+      <c r="T8" t="n">
+        <v>38.2426362130867</v>
+      </c>
+      <c r="U8" t="n">
+        <v>44.4525737623892</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-7.98429052617551</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7.98429052617551</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-8.81497792845377</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.924337957124842</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.07671850569566</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-14.3731187850755</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>8.16318123577304</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.924337957124842</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.975</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -44,88 +44,88 @@
     <t xml:space="preserve">Venue</t>
   </si>
   <si>
+    <t xml:space="preserve">north melbourne</t>
+  </si>
+  <si>
     <t xml:space="preserve">western bulldogs</t>
   </si>
   <si>
+    <t xml:space="preserve">Previous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Tasmania Stadium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adelaide crows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">waalitj marawar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Farms Oval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney swans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st kilda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.ex Coffs International Stadium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">greater western sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">port adelaide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corroboree Group Oval Manuka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane lions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casey Fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast suns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geelong cats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">People First Stadium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collingwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hawthorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victoria Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fremantle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carlton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cockburn ARC Oval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">essendon</t>
+  </si>
+  <si>
     <t xml:space="preserve">richmond</t>
   </si>
   <si>
-    <t xml:space="preserve">Provisional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mission Whitten Oval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">west coast eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast suns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mineral Resources Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geelong cats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st kilda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GMHBA Stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane lions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brighton Homes Arena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney swans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">essendon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collingwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fremantle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victoria Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">greater western sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casey Fields</t>
-  </si>
-  <si>
-    <t xml:space="preserve">carlton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adelaide crows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IKON Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">port adelaide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hawthorn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alberton Oval</t>
+    <t xml:space="preserve">TIO Stadium</t>
   </si>
 </sst>
 </file>
@@ -461,15 +461,15 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="22.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="19.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="26.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="22.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="32.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,7 +506,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -521,16 +521,16 @@
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.7</v>
+        <v>-61.6</v>
       </c>
       <c r="G2" t="n">
-        <v>-13</v>
+        <v>-19.9</v>
       </c>
       <c r="H2" t="n">
-        <v>-14.6</v>
+        <v>-69.4</v>
       </c>
       <c r="I2" t="n">
-        <v>76</v>
+        <v>80.4</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -553,16 +553,16 @@
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.9</v>
+        <v>-37.5</v>
       </c>
       <c r="G3" t="n">
-        <v>-16.8</v>
+        <v>-6.2</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.8</v>
+        <v>-34.6</v>
       </c>
       <c r="I3" t="n">
-        <v>80.8</v>
+        <v>83</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -585,16 +585,16 @@
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>-13.6</v>
+        <v>-35.7</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.7</v>
+        <v>-6.8</v>
       </c>
       <c r="H4" t="n">
-        <v>-17.8</v>
+        <v>-39.4</v>
       </c>
       <c r="I4" t="n">
-        <v>81.1</v>
+        <v>80.4</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -602,7 +602,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46256</v>
+        <v>46264</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -617,16 +617,16 @@
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>24</v>
+        <v>16.2</v>
       </c>
       <c r="G5" t="n">
-        <v>11.2</v>
+        <v>13.6</v>
       </c>
       <c r="H5" t="n">
-        <v>26.9</v>
+        <v>14.6</v>
       </c>
       <c r="I5" t="n">
-        <v>87.1</v>
+        <v>96.5</v>
       </c>
       <c r="J5" t="s">
         <v>22</v>
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -649,16 +649,16 @@
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>-19.6</v>
+        <v>-1.6</v>
       </c>
       <c r="G6" t="n">
-        <v>-10.5</v>
+        <v>-1.4</v>
       </c>
       <c r="H6" t="n">
-        <v>-21.9</v>
+        <v>-7.6</v>
       </c>
       <c r="I6" t="n">
-        <v>78.4</v>
+        <v>87.9</v>
       </c>
       <c r="J6" t="s">
         <v>25</v>
@@ -666,7 +666,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -681,16 +681,16 @@
         <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>12.3</v>
+        <v>7.3</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>13.9</v>
       </c>
       <c r="H7" t="n">
-        <v>14.3</v>
+        <v>1.4</v>
       </c>
       <c r="I7" t="n">
-        <v>71.3</v>
+        <v>87.1</v>
       </c>
       <c r="J7" t="s">
         <v>28</v>
@@ -698,7 +698,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
@@ -713,16 +713,16 @@
         <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>-40.4</v>
+        <v>-5.7</v>
       </c>
       <c r="G8" t="n">
-        <v>-25.2</v>
+        <v>5.4</v>
       </c>
       <c r="H8" t="n">
-        <v>-44.8</v>
+        <v>-8.8</v>
       </c>
       <c r="I8" t="n">
-        <v>90.1</v>
+        <v>73.7</v>
       </c>
       <c r="J8" t="s">
         <v>31</v>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
@@ -745,16 +745,16 @@
         <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>7.4</v>
+        <v>-10.3</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.5</v>
+        <v>4.6</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2</v>
+        <v>-10.7</v>
       </c>
       <c r="I9" t="n">
-        <v>87.5</v>
+        <v>82.4</v>
       </c>
       <c r="J9" t="s">
         <v>34</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B10" t="s">
         <v>35</v>
@@ -777,16 +777,16 @@
         <v>12</v>
       </c>
       <c r="F10" t="n">
-        <v>-12.3</v>
+        <v>-12.6</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.9</v>
+        <v>0.4</v>
       </c>
       <c r="H10" t="n">
-        <v>-12.9</v>
+        <v>-20.4</v>
       </c>
       <c r="I10" t="n">
-        <v>89.5</v>
+        <v>75.4</v>
       </c>
       <c r="J10" t="s">
         <v>37</v>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,40 +44,13 @@
     <t xml:space="preserve">Venue</t>
   </si>
   <si>
-    <t xml:space="preserve">north melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">western bulldogs</t>
+    <t xml:space="preserve">greater western sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">port adelaide</t>
   </si>
   <si>
     <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University of Tasmania Stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adelaide crows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">waalitj marawar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Farms Oval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney swans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st kilda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C.ex Coffs International Stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">greater western sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">port adelaide</t>
   </si>
   <si>
     <t xml:space="preserve">Corroboree Group Oval Manuka</t>
@@ -462,14 +435,14 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="14.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="19.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="26.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="32.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="28.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,7 +479,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -521,16 +494,16 @@
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>-61.6</v>
+        <v>16.2</v>
       </c>
       <c r="G2" t="n">
-        <v>-19.9</v>
+        <v>13.6</v>
       </c>
       <c r="H2" t="n">
-        <v>-69.4</v>
+        <v>14.6</v>
       </c>
       <c r="I2" t="n">
-        <v>80.4</v>
+        <v>96.5</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -538,7 +511,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -553,16 +526,16 @@
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>-37.5</v>
+        <v>-1.6</v>
       </c>
       <c r="G3" t="n">
-        <v>-6.2</v>
+        <v>-1.4</v>
       </c>
       <c r="H3" t="n">
-        <v>-34.6</v>
+        <v>-7.6</v>
       </c>
       <c r="I3" t="n">
-        <v>83</v>
+        <v>87.9</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -570,7 +543,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -585,16 +558,16 @@
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>-35.7</v>
+        <v>7.3</v>
       </c>
       <c r="G4" t="n">
-        <v>-6.8</v>
+        <v>13.9</v>
       </c>
       <c r="H4" t="n">
-        <v>-39.4</v>
+        <v>1.4</v>
       </c>
       <c r="I4" t="n">
-        <v>80.4</v>
+        <v>87.1</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -617,16 +590,16 @@
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>16.2</v>
+        <v>-5.7</v>
       </c>
       <c r="G5" t="n">
-        <v>13.6</v>
+        <v>5.4</v>
       </c>
       <c r="H5" t="n">
-        <v>14.6</v>
+        <v>-8.8</v>
       </c>
       <c r="I5" t="n">
-        <v>96.5</v>
+        <v>73.7</v>
       </c>
       <c r="J5" t="s">
         <v>22</v>
@@ -649,16 +622,16 @@
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6</v>
+        <v>-10.3</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4</v>
+        <v>4.6</v>
       </c>
       <c r="H6" t="n">
-        <v>-7.6</v>
+        <v>-10.7</v>
       </c>
       <c r="I6" t="n">
-        <v>87.9</v>
+        <v>82.4</v>
       </c>
       <c r="J6" t="s">
         <v>25</v>
@@ -681,115 +654,19 @@
         <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>7.3</v>
+        <v>-12.6</v>
       </c>
       <c r="G7" t="n">
-        <v>13.9</v>
+        <v>0.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4</v>
+        <v>-20.4</v>
       </c>
       <c r="I7" t="n">
-        <v>87.1</v>
+        <v>75.4</v>
       </c>
       <c r="J7" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46264</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-8.8</v>
-      </c>
-      <c r="I8" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="J8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46264</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>82.4</v>
-      </c>
-      <c r="J9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46264</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-12.6</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-20.4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>75.4</v>
-      </c>
-      <c r="J10" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,61 +44,85 @@
     <t xml:space="preserve">Venue</t>
   </si>
   <si>
+    <t xml:space="preserve">western bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney swans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mission Whitten Oval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st kilda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSEA Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">port adelaide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast suns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alberton Oval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane lions</t>
+  </si>
+  <si>
     <t xml:space="preserve">greater western sydney</t>
   </si>
   <si>
-    <t xml:space="preserve">port adelaide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corroboree Group Oval Manuka</t>
+    <t xml:space="preserve">Brighton Homes Arena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">richmond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fremantle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IKON Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hawthorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adelaide crows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kennedy Community Centre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geelong cats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">essendon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMHBA Stadium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carlton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collingwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">waalitj marawar</t>
   </si>
   <si>
     <t xml:space="preserve">melbourne</t>
   </si>
   <si>
-    <t xml:space="preserve">brisbane lions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casey Fields</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast suns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geelong cats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">People First Stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collingwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hawthorn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victoria Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fremantle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">carlton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cockburn ARC Oval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">essendon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">richmond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIO Stadium</t>
+    <t xml:space="preserve">Mineral Resources Park</t>
   </si>
 </sst>
 </file>
@@ -434,15 +458,15 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="14.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="22.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="19.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="26.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="28.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="24.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,7 +503,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46264</v>
+        <v>46270</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -494,16 +518,16 @@
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>16.2</v>
+        <v>16.7</v>
       </c>
       <c r="G2" t="n">
-        <v>13.6</v>
+        <v>-6.5</v>
       </c>
       <c r="H2" t="n">
-        <v>14.6</v>
+        <v>20.5</v>
       </c>
       <c r="I2" t="n">
-        <v>96.5</v>
+        <v>79.3</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -511,7 +535,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46264</v>
+        <v>46270</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -526,16 +550,16 @@
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.4</v>
+        <v>29.6</v>
       </c>
       <c r="H3" t="n">
-        <v>-7.6</v>
+        <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>87.9</v>
+        <v>81.4</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -543,7 +567,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46264</v>
+        <v>46270</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -558,16 +582,16 @@
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>7.3</v>
+        <v>-10.1</v>
       </c>
       <c r="G4" t="n">
-        <v>13.9</v>
+        <v>-21.3</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4</v>
+        <v>-7.3</v>
       </c>
       <c r="I4" t="n">
-        <v>87.1</v>
+        <v>94.8</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -575,7 +599,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46264</v>
+        <v>46270</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -590,16 +614,16 @@
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.7</v>
+        <v>-41.6</v>
       </c>
       <c r="G5" t="n">
-        <v>5.4</v>
+        <v>-25.7</v>
       </c>
       <c r="H5" t="n">
-        <v>-8.8</v>
+        <v>-43.7</v>
       </c>
       <c r="I5" t="n">
-        <v>73.7</v>
+        <v>89.4</v>
       </c>
       <c r="J5" t="s">
         <v>22</v>
@@ -607,7 +631,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -622,16 +646,16 @@
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>-10.3</v>
+        <v>26.3</v>
       </c>
       <c r="G6" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H6" t="n">
-        <v>-10.7</v>
+        <v>35.1</v>
       </c>
       <c r="I6" t="n">
-        <v>82.4</v>
+        <v>75.6</v>
       </c>
       <c r="J6" t="s">
         <v>25</v>
@@ -639,7 +663,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -654,19 +678,115 @@
         <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>-12.6</v>
+        <v>12.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4</v>
+        <v>3.9</v>
       </c>
       <c r="H7" t="n">
-        <v>-20.4</v>
+        <v>15.9</v>
       </c>
       <c r="I7" t="n">
-        <v>75.4</v>
+        <v>80.4</v>
       </c>
       <c r="J7" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-8.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>79.9</v>
+      </c>
+      <c r="J8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-25.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="J9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>86.1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,49 +44,13 @@
     <t xml:space="preserve">Venue</t>
   </si>
   <si>
-    <t xml:space="preserve">western bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney swans</t>
+    <t xml:space="preserve">richmond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fremantle</t>
   </si>
   <si>
     <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mission Whitten Oval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st kilda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSEA Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">port adelaide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast suns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alberton Oval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane lions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">greater western sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brighton Homes Arena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">richmond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fremantle</t>
   </si>
   <si>
     <t xml:space="preserve">IKON Park</t>
@@ -458,8 +422,8 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="22.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="15.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="14.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="19.71" hidden="0" customWidth="1"/>
@@ -503,7 +467,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -518,16 +482,16 @@
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>16.7</v>
+        <v>26.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-6.5</v>
+        <v>4.9</v>
       </c>
       <c r="H2" t="n">
-        <v>20.5</v>
+        <v>35.1</v>
       </c>
       <c r="I2" t="n">
-        <v>79.3</v>
+        <v>75.6</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -535,7 +499,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -550,16 +514,16 @@
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="G3" t="n">
-        <v>29.6</v>
+        <v>3.9</v>
       </c>
       <c r="H3" t="n">
-        <v>48.2</v>
+        <v>15.9</v>
       </c>
       <c r="I3" t="n">
-        <v>81.4</v>
+        <v>80.4</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -567,7 +531,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -582,16 +546,16 @@
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>-10.1</v>
+        <v>-9.6</v>
       </c>
       <c r="G4" t="n">
-        <v>-21.3</v>
+        <v>-8.3</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.3</v>
+        <v>-5.3</v>
       </c>
       <c r="I4" t="n">
-        <v>94.8</v>
+        <v>79.9</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -599,7 +563,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -614,19 +578,19 @@
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>-41.6</v>
+        <v>-20.8</v>
       </c>
       <c r="G5" t="n">
-        <v>-25.7</v>
+        <v>-13.1</v>
       </c>
       <c r="H5" t="n">
-        <v>-43.7</v>
+        <v>-25.3</v>
       </c>
       <c r="I5" t="n">
-        <v>89.4</v>
+        <v>80.8</v>
       </c>
       <c r="J5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -634,159 +598,31 @@
         <v>46271</v>
       </c>
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>86.1</v>
+      </c>
+      <c r="J6" t="s">
         <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H6" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>75.6</v>
-      </c>
-      <c r="J6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>80.4</v>
-      </c>
-      <c r="J7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-9.6</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-8.3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>79.9</v>
-      </c>
-      <c r="J8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-20.8</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-13.1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-25.3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="J9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="G10" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H10" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="I10" t="n">
-        <v>86.1</v>
-      </c>
-      <c r="J10" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,36 +12,192 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Team List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Team List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROD Projected Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM-only Projected Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLAYER-only Projected Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projected Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venue</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+  <si>
+    <t xml:space="preserve">rating_as_of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_datetime_utc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model_version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected_margin_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prod_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prod_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">previous_prod_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_only_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_only_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_home_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_away_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hybrid_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hybrid_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hybrid_weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">binary_preferred_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">binary_preferred_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">significant_change_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_team_disagreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_lineup_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_lineup_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_team_list_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_team_list_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cold_start_players</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_team_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_player_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_lineup_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_team_lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_player_lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_decay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-05T02:35:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">western bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney swans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mission Whitten Oval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aflw_joint_club_persistent_player_margin_prod_1.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOINT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-05T03:05:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st kilda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSEA Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-05T04:35:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">port adelaide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast suns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alberton Oval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-05T08:35:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane lions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">greater western sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brighton Homes Arena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06T02:30:00.000+0000</t>
   </si>
   <si>
     <t xml:space="preserve">richmond</t>
@@ -50,12 +206,12 @@
     <t xml:space="preserve">fremantle</t>
   </si>
   <si>
-    <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
     <t xml:space="preserve">IKON Park</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-09-06T03:05:00.000+0000</t>
+  </si>
+  <si>
     <t xml:space="preserve">hawthorn</t>
   </si>
   <si>
@@ -65,6 +221,9 @@
     <t xml:space="preserve">Kennedy Community Centre</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-09-06T04:35:00.000+0000</t>
+  </si>
+  <si>
     <t xml:space="preserve">geelong cats</t>
   </si>
   <si>
@@ -74,10 +233,16 @@
     <t xml:space="preserve">GMHBA Stadium</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-09-06T05:05:00.000+0000</t>
+  </si>
+  <si>
     <t xml:space="preserve">carlton</t>
   </si>
   <si>
     <t xml:space="preserve">collingwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06T07:05:00.000+0000</t>
   </si>
   <si>
     <t xml:space="preserve">waalitj marawar</t>
@@ -421,16 +586,47 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="15.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="14.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="19.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="5.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="16.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="26.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="24.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="51.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="21.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="14.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="12.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="15.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="20.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="16.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="19.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="18.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="21.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="15.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="20.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="20.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="13.71" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="16.71" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="13.71" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="22.71" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="23.71" hidden="0" customWidth="1"/>
+    <col min="27" max="27" width="15.71" hidden="0" customWidth="1"/>
+    <col min="28" max="28" width="23.71" hidden="0" customWidth="1"/>
+    <col min="29" max="29" width="24.71" hidden="0" customWidth="1"/>
+    <col min="30" max="30" width="18.71" hidden="0" customWidth="1"/>
+    <col min="31" max="31" width="18.71" hidden="0" customWidth="1"/>
+    <col min="32" max="32" width="21.71" hidden="0" customWidth="1"/>
+    <col min="33" max="33" width="21.71" hidden="0" customWidth="1"/>
+    <col min="34" max="34" width="18.71" hidden="0" customWidth="1"/>
+    <col min="35" max="35" width="14.71" hidden="0" customWidth="1"/>
+    <col min="36" max="36" width="20.71" hidden="0" customWidth="1"/>
+    <col min="37" max="37" width="22.71" hidden="0" customWidth="1"/>
+    <col min="38" max="38" width="21.71" hidden="0" customWidth="1"/>
+    <col min="39" max="39" width="17.71" hidden="0" customWidth="1"/>
+    <col min="40" max="40" width="19.71" hidden="0" customWidth="1"/>
+    <col min="41" max="41" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,165 +660,1223 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
+        <v>46267</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>46270</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
+        <v>41</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>75.6</v>
-      </c>
-      <c r="J2" t="s">
-        <v>13</v>
+        <v>42</v>
+      </c>
+      <c r="F2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-16.6723116574329</v>
+      </c>
+      <c r="K2" t="n">
+        <v>16.6723116574329</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-16.6723116574329</v>
+      </c>
+      <c r="M2" t="n">
+        <v>16.6723116574329</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-16.6723116574329</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6.49130058167378</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-6.49130058167378</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-20.5003490396832</v>
+      </c>
+      <c r="R2" t="n">
+        <v>20.5003490396832</v>
+      </c>
+      <c r="S2" t="n">
+        <v>79.2701169519064</v>
+      </c>
+      <c r="T2" t="n">
+        <v>31.2989026472368</v>
+      </c>
+      <c r="U2" t="n">
+        <v>47.9712143046696</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-4.305359266869</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4.305359266869</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>6.49130058167378</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-26.9916496213569</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>19.0011739064417</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-35.6734855638746</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
+        <v>46267</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>46270</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
+        <v>49</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="I3" t="n">
-        <v>80.4</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
+        <v>50</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-50.0021167397785</v>
+      </c>
+      <c r="K3" t="n">
+        <v>50.0021167397785</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-50.0021167397785</v>
+      </c>
+      <c r="M3" t="n">
+        <v>50.0021167397785</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-50.0021167397785</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-29.6076094185119</v>
+      </c>
+      <c r="P3" t="n">
+        <v>29.6076094185119</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-48.2291058740438</v>
+      </c>
+      <c r="R3" t="n">
+        <v>48.2291058740438</v>
+      </c>
+      <c r="S3" t="n">
+        <v>81.4192293925257</v>
+      </c>
+      <c r="T3" t="n">
+        <v>15.7085563263736</v>
+      </c>
+      <c r="U3" t="n">
+        <v>65.7106730661521</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-37.0562080007246</v>
+      </c>
+      <c r="W3" t="n">
+        <v>37.0562080007246</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-29.6076094185119</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-18.6214964555319</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-12.7683188024278</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-37.2337979373507</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
+        <v>46267</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46270</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
+        <v>53</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-9.6</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-8.3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>79.9</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10.0928623377394</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-10.0928623377394</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10.0928623377394</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-10.0928623377394</v>
+      </c>
+      <c r="N4" t="n">
+        <v>10.0928623377394</v>
+      </c>
+      <c r="O4" t="n">
+        <v>21.2906999548106</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-21.2906999548106</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7.2501341881087</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-7.2501341881087</v>
+      </c>
+      <c r="S4" t="n">
+        <v>94.817699488872</v>
+      </c>
+      <c r="T4" t="n">
+        <v>52.4552809133057</v>
+      </c>
+      <c r="U4" t="n">
+        <v>42.3624185755663</v>
+      </c>
+      <c r="V4" t="n">
+        <v>15.6744736481299</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-15.6744736481299</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>21.2906999548106</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-14.0405657667019</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>20.0466535244546</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-9.95379118671522</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
+        <v>46267</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46270</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
+        <v>57</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-20.8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-13.1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-25.3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="J5" t="s">
-        <v>13</v>
+        <v>58</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" t="n">
+        <v>41.5593586571489</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-41.5593586571489</v>
+      </c>
+      <c r="L5" t="n">
+        <v>41.5593586571489</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-41.5593586571489</v>
+      </c>
+      <c r="N5" t="n">
+        <v>41.5593586571489</v>
+      </c>
+      <c r="O5" t="n">
+        <v>25.6816201629175</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-25.6816201629175</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>43.729899197013</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-43.729899197013</v>
+      </c>
+      <c r="S5" t="n">
+        <v>89.4322741320656</v>
+      </c>
+      <c r="T5" t="n">
+        <v>65.4958163946073</v>
+      </c>
+      <c r="U5" t="n">
+        <v>23.9364577374583</v>
+      </c>
+      <c r="V5" t="n">
+        <v>32.9009317765557</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-32.9009317765557</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>25.6816201629175</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>18.0482790340955</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>23.9235751514064</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>17.6357835057426</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B6" s="1" t="n">
         <v>46271</v>
       </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
       <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
+        <v>61</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H6" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="I6" t="n">
-        <v>86.1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>24</v>
+        <v>62</v>
+      </c>
+      <c r="F6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-26.281096855093</v>
+      </c>
+      <c r="K6" t="n">
+        <v>26.281096855093</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-26.281096855093</v>
+      </c>
+      <c r="M6" t="n">
+        <v>26.281096855093</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-26.281096855093</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-4.85735375987388</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.85735375987388</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-35.1474421602214</v>
+      </c>
+      <c r="R6" t="n">
+        <v>35.1474421602214</v>
+      </c>
+      <c r="S6" t="n">
+        <v>75.6128499791106</v>
+      </c>
+      <c r="T6" t="n">
+        <v>24.6658765620088</v>
+      </c>
+      <c r="U6" t="n">
+        <v>50.9469734171018</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-16.8573537598739</v>
+      </c>
+      <c r="W6" t="n">
+        <v>16.8573537598739</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-4.85735375987388</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-30.2900884003475</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>10.6416328138489</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-36.922729668942</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-12.5325798466577</v>
+      </c>
+      <c r="K7" t="n">
+        <v>12.5325798466577</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-12.5325798466577</v>
+      </c>
+      <c r="M7" t="n">
+        <v>12.5325798466577</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-12.5325798466577</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-3.8825905363434</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.8825905363434</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-15.9473836994724</v>
+      </c>
+      <c r="R7" t="n">
+        <v>15.9473836994724</v>
+      </c>
+      <c r="S7" t="n">
+        <v>80.433498880422</v>
+      </c>
+      <c r="T7" t="n">
+        <v>33.9504595168821</v>
+      </c>
+      <c r="U7" t="n">
+        <v>46.4830393635399</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-8.708507801595</v>
+      </c>
+      <c r="W7" t="n">
+        <v>8.708507801595</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-3.8825905363434</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-12.064793163129</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-4.01397662540538</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-8.51860322125237</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" t="n">
+        <v>9.59707361041435</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-9.59707361041435</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9.59707361041435</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-9.59707361041435</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9.59707361041435</v>
+      </c>
+      <c r="O8" t="n">
+        <v>8.27654763017873</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-8.27654763017873</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.34668154333982</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-5.34668154333982</v>
+      </c>
+      <c r="S8" t="n">
+        <v>79.8531515887037</v>
+      </c>
+      <c r="T8" t="n">
+        <v>44.725112599559</v>
+      </c>
+      <c r="U8" t="n">
+        <v>35.1280389891447</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7.10460119544316</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-7.10460119544316</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>8.27654763017873</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-2.92986608683891</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>11.2056194355094</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-1.60854582509501</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.8019978694437</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-20.8019978694437</v>
+      </c>
+      <c r="L9" t="n">
+        <v>20.8019978694437</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-20.8019978694437</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20.8019978694437</v>
+      </c>
+      <c r="O9" t="n">
+        <v>13.0966047474696</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-13.0966047474696</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>25.3312894518126</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-25.3312894518126</v>
+      </c>
+      <c r="S9" t="n">
+        <v>80.8036813990586</v>
+      </c>
+      <c r="T9" t="n">
+        <v>50.8028396342512</v>
+      </c>
+      <c r="U9" t="n">
+        <v>30.0008417648075</v>
+      </c>
+      <c r="V9" t="n">
+        <v>17.9904786292068</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-17.9904786292068</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>13.0966047474696</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>12.234684704343</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>8.03721059632712</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>12.7647872731165</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-43.5752269240772</v>
+      </c>
+      <c r="K10" t="n">
+        <v>43.5752269240772</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-43.5752269240772</v>
+      </c>
+      <c r="M10" t="n">
+        <v>43.5752269240772</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-43.5752269240772</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-9.89601969839015</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9.89601969839015</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-41.8606596114241</v>
+      </c>
+      <c r="R10" t="n">
+        <v>41.8606596114241</v>
+      </c>
+      <c r="S10" t="n">
+        <v>86.0832115136059</v>
+      </c>
+      <c r="T10" t="n">
+        <v>21.2539922947644</v>
+      </c>
+      <c r="U10" t="n">
+        <v>64.8292192188415</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-21.8960196983901</v>
+      </c>
+      <c r="W10" t="n">
+        <v>21.8960196983901</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-9.89601969839015</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-31.9646399130339</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-11.7002847567502</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-31.8749421673269</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.975</v>
       </c>
     </row>
   </sheetData>
